--- a/Plotting/production_shares_olefins_scope.xlsx
+++ b/Plotting/production_shares_olefins_scope.xlsx
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1910550.410209683</v>
+        <v>1910550.410209645</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -551,7 +551,7 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>619640.9435081835</v>
       </c>
     </row>
     <row r="8">
@@ -580,10 +580,10 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>872186.8952793099</v>
+        <v>701009.3413982852</v>
       </c>
       <c r="D9" t="n">
-        <v>392156.5133670096</v>
+        <v>169834.2954574953</v>
       </c>
     </row>
     <row r="10">
@@ -596,10 +596,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>1037502.618801572</v>
+        <v>1102369.149665265</v>
       </c>
       <c r="D10" t="n">
-        <v>1517523.486632992</v>
+        <v>1120333.279155937</v>
       </c>
     </row>
     <row r="11">
@@ -612,7 +612,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>17797.85136556534</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -628,7 +628,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>88503.65757088189</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
